--- a/hltv team/hltv stats team for event.xlsx
+++ b/hltv team/hltv stats team for event.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\10725\Desktop\hltv\hltv team\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B30DC82-F2EF-4709-953A-450B788AA97F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7C8B133-1193-42A5-A770-5B4016B02136}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="34">
   <si>
     <t>队名</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -91,34 +91,59 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>FaZe</t>
-  </si>
-  <si>
-    <t>Natus Vincere</t>
-  </si>
-  <si>
-    <t>Spirit</t>
-  </si>
-  <si>
-    <t>FURIA</t>
-  </si>
-  <si>
-    <t>The MongolZ</t>
-  </si>
-  <si>
-    <t>Falcons</t>
-  </si>
-  <si>
-    <t>Vitality</t>
-  </si>
-  <si>
-    <t>MOUZ</t>
+    <t>BetBoom</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>SL布达佩斯Major淘汰赛 各项团队数据 Made by @Viston</t>
+    <t>PARIVISION</t>
+  </si>
+  <si>
+    <t>FaZe</t>
+  </si>
+  <si>
+    <t>Alliance</t>
+  </si>
+  <si>
+    <t>TYLOO</t>
+  </si>
+  <si>
+    <t>BIG</t>
+  </si>
+  <si>
+    <t>Nemesis</t>
+  </si>
+  <si>
+    <t>MIBR</t>
+  </si>
+  <si>
+    <t>EYEBALLERS</t>
+  </si>
+  <si>
+    <t>B8</t>
+  </si>
+  <si>
+    <t>Ninjas in Pyjamas</t>
+  </si>
+  <si>
+    <t>Lynn Vision</t>
+  </si>
+  <si>
+    <t>3DMAX</t>
+  </si>
+  <si>
+    <t>Luminosity</t>
+  </si>
+  <si>
+    <t>SINNERS</t>
+  </si>
+  <si>
+    <t>XPL广州站 各项团队数据 Made by @Viston</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9z</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -568,7 +593,7 @@
   <sheetData>
     <row r="1" spans="1:35" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -794,100 +819,100 @@
     </row>
     <row r="5" spans="1:35" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="B5" s="2">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C5" s="3">
-        <v>0.628</v>
+        <v>0.54900000000000004</v>
       </c>
       <c r="D5" s="3">
-        <v>0.56699999999999995</v>
+        <v>0.48199999999999998</v>
       </c>
       <c r="E5" s="4">
-        <v>0.88</v>
+        <v>0.79</v>
       </c>
       <c r="F5" s="3">
-        <v>0.78500000000000003</v>
+        <v>0.73599999999999999</v>
       </c>
       <c r="G5" s="3">
-        <v>0.42299999999999999</v>
+        <v>0.372</v>
       </c>
       <c r="H5" s="3">
-        <v>0.2</v>
+        <v>0.221</v>
       </c>
       <c r="I5" s="2">
-        <v>25.7</v>
+        <v>18</v>
       </c>
       <c r="J5" s="2">
-        <v>0.34</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="K5" s="3">
         <v>0.5</v>
       </c>
       <c r="L5" s="3">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="M5" s="3">
         <v>0.125</v>
       </c>
       <c r="N5" s="3">
-        <v>0.60299999999999998</v>
+        <v>0.59099999999999997</v>
       </c>
       <c r="O5" s="3">
-        <v>0.65400000000000003</v>
+        <v>0.55900000000000005</v>
       </c>
       <c r="P5" s="2">
-        <v>1.01</v>
+        <v>0.9</v>
       </c>
       <c r="Q5" s="3">
-        <v>0.72499999999999998</v>
+        <v>0.74</v>
       </c>
       <c r="R5" s="3">
-        <v>0.37</v>
+        <v>0.40200000000000002</v>
       </c>
       <c r="S5" s="3">
-        <v>0.158</v>
+        <v>0.251</v>
       </c>
       <c r="T5" s="2">
-        <v>35.4</v>
+        <v>22.9</v>
       </c>
       <c r="U5" s="2">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
       <c r="V5" s="3">
         <v>0.5</v>
       </c>
       <c r="W5" s="3">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="X5" s="3">
         <v>0.25</v>
       </c>
       <c r="Y5" s="3">
-        <v>0.65100000000000002</v>
+        <v>0.50600000000000001</v>
       </c>
       <c r="Z5" s="3">
-        <v>0.48799999999999999</v>
+        <v>0.40200000000000002</v>
       </c>
       <c r="AA5" s="2">
-        <v>0.77</v>
+        <v>0.68</v>
       </c>
       <c r="AB5" s="3">
-        <v>0.85699999999999998</v>
+        <v>0.73</v>
       </c>
       <c r="AC5" s="3">
-        <v>0.45500000000000002</v>
+        <v>0.34899999999999998</v>
       </c>
       <c r="AD5" s="3">
-        <v>0.23300000000000001</v>
+        <v>0.19600000000000001</v>
       </c>
       <c r="AE5" s="2">
-        <v>16.899999999999999</v>
+        <v>12.9</v>
       </c>
       <c r="AF5" s="2">
-        <v>0.41</v>
+        <v>0.26</v>
       </c>
       <c r="AG5" s="3">
         <v>0.5</v>
@@ -901,106 +926,106 @@
     </row>
     <row r="6" spans="1:35" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B6" s="2">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C6" s="3">
-        <v>0.48299999999999998</v>
+        <v>0.52500000000000002</v>
       </c>
       <c r="D6" s="3">
-        <v>0.53400000000000003</v>
+        <v>0.52200000000000002</v>
       </c>
       <c r="E6" s="4">
-        <v>0.78</v>
+        <v>0.76</v>
       </c>
       <c r="F6" s="3">
-        <v>0.64500000000000002</v>
+        <v>0.69799999999999995</v>
       </c>
       <c r="G6" s="3">
-        <v>0.29599999999999999</v>
+        <v>0.33700000000000002</v>
       </c>
       <c r="H6" s="3">
-        <v>0.214</v>
+        <v>0.193</v>
       </c>
       <c r="I6" s="2">
-        <v>23.9</v>
+        <v>22.2</v>
       </c>
       <c r="J6" s="2">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="K6" s="3">
-        <v>0.66700000000000004</v>
+        <v>0.53300000000000003</v>
       </c>
       <c r="L6" s="3">
-        <v>0.83299999999999996</v>
+        <v>0.875</v>
       </c>
       <c r="M6" s="3">
-        <v>0</v>
+        <v>7.0999999999999994E-2</v>
       </c>
       <c r="N6" s="3">
-        <v>0.47499999999999998</v>
+        <v>0.503</v>
       </c>
       <c r="O6" s="3">
-        <v>0.63400000000000001</v>
+        <v>0.59299999999999997</v>
       </c>
       <c r="P6" s="2">
-        <v>0.83</v>
+        <v>0.81</v>
       </c>
       <c r="Q6" s="3">
-        <v>0.60899999999999999</v>
+        <v>0.67700000000000005</v>
       </c>
       <c r="R6" s="3">
-        <v>0.24299999999999999</v>
+        <v>0.25700000000000001</v>
       </c>
       <c r="S6" s="3">
-        <v>0.189</v>
+        <v>0.186</v>
       </c>
       <c r="T6" s="2">
-        <v>28.7</v>
+        <v>26.7</v>
       </c>
       <c r="U6" s="2">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="V6" s="3">
-        <v>0.66700000000000004</v>
+        <v>0.53300000000000003</v>
       </c>
       <c r="W6" s="3">
-        <v>0.83299999999999996</v>
+        <v>0.875</v>
       </c>
       <c r="X6" s="3">
-        <v>0</v>
+        <v>0.14299999999999999</v>
       </c>
       <c r="Y6" s="3">
-        <v>0.49299999999999999</v>
+        <v>0.54500000000000004</v>
       </c>
       <c r="Z6" s="3">
-        <v>0.39700000000000002</v>
+        <v>0.45500000000000002</v>
       </c>
       <c r="AA6" s="2">
         <v>0.7</v>
       </c>
       <c r="AB6" s="3">
-        <v>0.72399999999999998</v>
+        <v>0.72499999999999998</v>
       </c>
       <c r="AC6" s="3">
-        <v>0.34100000000000003</v>
+        <v>0.39600000000000002</v>
       </c>
       <c r="AD6" s="3">
-        <v>0.24299999999999999</v>
+        <v>0.19900000000000001</v>
       </c>
       <c r="AE6" s="2">
-        <v>17.2</v>
+        <v>17.899999999999999</v>
       </c>
       <c r="AF6" s="2">
-        <v>0.3</v>
+        <v>0.16</v>
       </c>
       <c r="AG6" s="3">
-        <v>0.66700000000000004</v>
+        <v>0.53300000000000003</v>
       </c>
       <c r="AH6" s="3">
-        <v>0.83299999999999996</v>
+        <v>0.875</v>
       </c>
       <c r="AI6" s="3">
         <v>0</v>
@@ -1008,144 +1033,144 @@
     </row>
     <row r="7" spans="1:35" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B7" s="2">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C7" s="3">
-        <v>0.56299999999999994</v>
+        <v>0.58199999999999996</v>
       </c>
       <c r="D7" s="3">
-        <v>0.5</v>
+        <v>0.51600000000000001</v>
       </c>
       <c r="E7" s="4">
-        <v>0.82</v>
+        <v>0.91</v>
       </c>
       <c r="F7" s="3">
-        <v>0.81</v>
+        <v>0.747</v>
       </c>
       <c r="G7" s="3">
-        <v>0.317</v>
+        <v>0.40799999999999997</v>
       </c>
       <c r="H7" s="3">
-        <v>0.23100000000000001</v>
+        <v>0.22600000000000001</v>
       </c>
       <c r="I7" s="2">
-        <v>23.3</v>
+        <v>21.2</v>
       </c>
       <c r="J7" s="2">
-        <v>0.34</v>
+        <v>0.26</v>
       </c>
       <c r="K7" s="3">
-        <v>0.58299999999999996</v>
+        <v>0.60699999999999998</v>
       </c>
       <c r="L7" s="3">
-        <v>0.85699999999999998</v>
+        <v>0.94099999999999995</v>
       </c>
       <c r="M7" s="3">
-        <v>0.4</v>
+        <v>0.182</v>
       </c>
       <c r="N7" s="3">
-        <v>0.64700000000000002</v>
+        <v>0.57299999999999995</v>
       </c>
       <c r="O7" s="3">
-        <v>0.64700000000000002</v>
+        <v>0.61099999999999999</v>
       </c>
       <c r="P7" s="2">
         <v>0.96</v>
       </c>
       <c r="Q7" s="3">
-        <v>0.81799999999999995</v>
+        <v>0.65600000000000003</v>
       </c>
       <c r="R7" s="3">
-        <v>0.33300000000000002</v>
+        <v>0.443</v>
       </c>
       <c r="S7" s="3">
-        <v>0.22800000000000001</v>
+        <v>0.23499999999999999</v>
       </c>
       <c r="T7" s="2">
-        <v>23.7</v>
+        <v>21.1</v>
       </c>
       <c r="U7" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="V7" s="3">
+        <v>0.71399999999999997</v>
+      </c>
+      <c r="W7" s="3">
+        <v>0.9</v>
+      </c>
+      <c r="X7" s="3">
         <v>0.25</v>
       </c>
-      <c r="V7" s="3">
-        <v>0.66700000000000004</v>
-      </c>
-      <c r="W7" s="3">
-        <v>1</v>
-      </c>
-      <c r="X7" s="3">
-        <v>0.5</v>
-      </c>
       <c r="Y7" s="3">
-        <v>0.50700000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="Z7" s="3">
-        <v>0.4</v>
+        <v>0.42399999999999999</v>
       </c>
       <c r="AA7" s="2">
-        <v>0.72</v>
+        <v>0.87</v>
       </c>
       <c r="AB7" s="3">
-        <v>0.8</v>
+        <v>0.871</v>
       </c>
       <c r="AC7" s="3">
-        <v>0.311</v>
+        <v>0.38500000000000001</v>
       </c>
       <c r="AD7" s="3">
-        <v>0.23300000000000001</v>
+        <v>0.218</v>
       </c>
       <c r="AE7" s="2">
-        <v>22.9</v>
+        <v>21.3</v>
       </c>
       <c r="AF7" s="2">
-        <v>0.4</v>
+        <v>0.31</v>
       </c>
       <c r="AG7" s="3">
         <v>0.5</v>
       </c>
       <c r="AH7" s="3">
-        <v>0.66700000000000004</v>
+        <v>1</v>
       </c>
       <c r="AI7" s="3">
-        <v>0.33300000000000002</v>
+        <v>0.14299999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:35" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B8" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C8" s="3">
-        <v>0.52900000000000003</v>
+        <v>0.53300000000000003</v>
       </c>
       <c r="D8" s="3">
-        <v>0.46100000000000002</v>
+        <v>0.54800000000000004</v>
       </c>
       <c r="E8" s="4">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="F8" s="3">
-        <v>0.78700000000000003</v>
+        <v>0.72</v>
       </c>
       <c r="G8" s="3">
         <v>0.309</v>
       </c>
       <c r="H8" s="3">
-        <v>0.21099999999999999</v>
+        <v>0.20200000000000001</v>
       </c>
       <c r="I8" s="2">
-        <v>22.2</v>
+        <v>31.3</v>
       </c>
       <c r="J8" s="2">
-        <v>0.24</v>
+        <v>0.27</v>
       </c>
       <c r="K8" s="3">
-        <v>0.625</v>
+        <v>0.54500000000000004</v>
       </c>
       <c r="L8" s="3">
         <v>1</v>
@@ -1154,31 +1179,31 @@
         <v>0</v>
       </c>
       <c r="N8" s="3">
-        <v>0.55600000000000005</v>
+        <v>0.55400000000000005</v>
       </c>
       <c r="O8" s="3">
-        <v>0.59299999999999997</v>
+        <v>0.58299999999999996</v>
       </c>
       <c r="P8" s="2">
-        <v>0.91</v>
+        <v>0.86</v>
       </c>
       <c r="Q8" s="3">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="R8" s="3">
-        <v>0.27300000000000002</v>
+        <v>0.35299999999999998</v>
       </c>
       <c r="S8" s="3">
-        <v>0.222</v>
+        <v>0.214</v>
       </c>
       <c r="T8" s="2">
-        <v>28.1</v>
+        <v>35.4</v>
       </c>
       <c r="U8" s="2">
         <v>0.28000000000000003</v>
       </c>
       <c r="V8" s="3">
-        <v>0.5</v>
+        <v>0.54500000000000004</v>
       </c>
       <c r="W8" s="3">
         <v>1</v>
@@ -1187,31 +1212,31 @@
         <v>0</v>
       </c>
       <c r="Y8" s="3">
-        <v>0.5</v>
+        <v>0.51200000000000001</v>
       </c>
       <c r="Z8" s="3">
-        <v>0.312</v>
+        <v>0.51200000000000001</v>
       </c>
       <c r="AA8" s="2">
         <v>0.69</v>
       </c>
       <c r="AB8" s="3">
-        <v>0.86699999999999999</v>
+        <v>0.74199999999999999</v>
       </c>
       <c r="AC8" s="3">
-        <v>0.33300000000000002</v>
+        <v>0.27100000000000002</v>
       </c>
       <c r="AD8" s="3">
-        <v>0.20100000000000001</v>
+        <v>0.193</v>
       </c>
       <c r="AE8" s="2">
-        <v>15.6</v>
+        <v>27.1</v>
       </c>
       <c r="AF8" s="2">
-        <v>0.19</v>
+        <v>0.26</v>
       </c>
       <c r="AG8" s="3">
-        <v>0.75</v>
+        <v>0.54500000000000004</v>
       </c>
       <c r="AH8" s="3">
         <v>1</v>
@@ -1222,106 +1247,106 @@
     </row>
     <row r="9" spans="1:35" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B9" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C9" s="3">
+        <v>0.57199999999999995</v>
+      </c>
+      <c r="D9" s="3">
+        <v>0.55100000000000005</v>
+      </c>
+      <c r="E9" s="4">
+        <v>0.77</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0.77900000000000003</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0.311</v>
+      </c>
+      <c r="H9" s="3">
+        <v>0.223</v>
+      </c>
+      <c r="I9" s="2">
+        <v>15.2</v>
+      </c>
+      <c r="J9" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="K9" s="3">
+        <v>0.64300000000000002</v>
+      </c>
+      <c r="L9" s="3">
+        <v>0.88900000000000001</v>
+      </c>
+      <c r="M9" s="3">
+        <v>0</v>
+      </c>
+      <c r="N9" s="3">
+        <v>0.65200000000000002</v>
+      </c>
+      <c r="O9" s="3">
+        <v>0.66700000000000004</v>
+      </c>
+      <c r="P9" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>0.77800000000000002</v>
+      </c>
+      <c r="R9" s="3">
         <v>0.38100000000000001</v>
       </c>
-      <c r="D9" s="3">
-        <v>0.47599999999999998</v>
-      </c>
-      <c r="E9" s="4">
-        <v>0.71</v>
-      </c>
-      <c r="F9" s="3">
-        <v>0.66700000000000004</v>
-      </c>
-      <c r="G9" s="3">
-        <v>0.121</v>
-      </c>
-      <c r="H9" s="3">
-        <v>0.13500000000000001</v>
-      </c>
-      <c r="I9" s="2">
-        <v>23.3</v>
-      </c>
-      <c r="J9" s="2">
-        <v>0.33</v>
-      </c>
-      <c r="K9" s="3">
-        <v>0.16700000000000001</v>
-      </c>
-      <c r="L9" s="3">
+      <c r="S9" s="3">
+        <v>0.23200000000000001</v>
+      </c>
+      <c r="T9" s="2">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="U9" s="2">
+        <v>0.17</v>
+      </c>
+      <c r="V9" s="3">
+        <v>0.71399999999999997</v>
+      </c>
+      <c r="W9" s="3">
+        <v>1</v>
+      </c>
+      <c r="X9" s="3">
         <v>0</v>
       </c>
-      <c r="M9" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="N9" s="3">
-        <v>0.436</v>
-      </c>
-      <c r="O9" s="3">
-        <v>0.59</v>
-      </c>
-      <c r="P9" s="2">
-        <v>0.82</v>
-      </c>
-      <c r="Q9" s="3">
-        <v>0.65200000000000002</v>
-      </c>
-      <c r="R9" s="3">
-        <v>0.125</v>
-      </c>
-      <c r="S9" s="3">
-        <v>0.13300000000000001</v>
-      </c>
-      <c r="T9" s="2">
-        <v>26.3</v>
-      </c>
-      <c r="U9" s="2">
-        <v>0.26</v>
-      </c>
-      <c r="V9" s="3">
-        <v>0</v>
-      </c>
-      <c r="W9" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="X9" s="3">
-        <v>0.33300000000000002</v>
-      </c>
       <c r="Y9" s="3">
-        <v>0.29199999999999998</v>
+        <v>0.5</v>
       </c>
       <c r="Z9" s="3">
-        <v>0.29199999999999998</v>
+        <v>0.44400000000000001</v>
       </c>
       <c r="AA9" s="2">
-        <v>0.54</v>
+        <v>0.6</v>
       </c>
       <c r="AB9" s="3">
-        <v>0.71399999999999997</v>
+        <v>0.78100000000000003</v>
       </c>
       <c r="AC9" s="3">
-        <v>0.11799999999999999</v>
+        <v>0.27500000000000002</v>
       </c>
       <c r="AD9" s="3">
-        <v>0.13700000000000001</v>
+        <v>0.217</v>
       </c>
       <c r="AE9" s="2">
-        <v>18.5</v>
+        <v>10.6</v>
       </c>
       <c r="AF9" s="2">
-        <v>0.46</v>
+        <v>0.22</v>
       </c>
       <c r="AG9" s="3">
-        <v>0.33300000000000002</v>
+        <v>0.57099999999999995</v>
       </c>
       <c r="AH9" s="3">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AI9" s="3">
         <v>0</v>
@@ -1329,216 +1354,216 @@
     </row>
     <row r="10" spans="1:35" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B10" s="2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C10" s="3">
-        <v>0.25700000000000001</v>
+        <v>0.48299999999999998</v>
       </c>
       <c r="D10" s="3">
-        <v>0.45700000000000002</v>
+        <v>0.56499999999999995</v>
       </c>
       <c r="E10" s="4">
-        <v>0.54</v>
+        <v>0.79</v>
       </c>
       <c r="F10" s="3">
-        <v>0.375</v>
+        <v>0.64900000000000002</v>
       </c>
       <c r="G10" s="3">
-        <v>0.158</v>
+        <v>0.26500000000000001</v>
       </c>
       <c r="H10" s="3">
-        <v>0.11</v>
+        <v>0.224</v>
       </c>
       <c r="I10" s="2">
-        <v>15.6</v>
+        <v>27.7</v>
       </c>
       <c r="J10" s="2">
-        <v>0.09</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="K10" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="L10" s="3">
+        <v>0.72699999999999998</v>
+      </c>
+      <c r="M10" s="3">
         <v>0</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="M10" s="3">
-        <v>0.5</v>
-      </c>
       <c r="N10" s="3">
-        <v>0.222</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="O10" s="3">
-        <v>0.44400000000000001</v>
+        <v>0.66900000000000004</v>
       </c>
       <c r="P10" s="2">
-        <v>0.72</v>
+        <v>0.91</v>
       </c>
       <c r="Q10" s="3">
-        <v>0.375</v>
+        <v>0.67700000000000005</v>
       </c>
       <c r="R10" s="3">
-        <v>0.1</v>
+        <v>0.29799999999999999</v>
       </c>
       <c r="S10" s="3">
-        <v>0.13300000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="T10" s="2">
-        <v>15.4</v>
+        <v>32.6</v>
       </c>
       <c r="U10" s="2">
-        <v>0.06</v>
+        <v>0.23</v>
       </c>
       <c r="V10" s="3">
+        <v>0.54500000000000004</v>
+      </c>
+      <c r="W10" s="3">
+        <v>1</v>
+      </c>
+      <c r="X10" s="3">
         <v>0</v>
       </c>
-      <c r="W10" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="X10" s="3">
-        <v>0.5</v>
-      </c>
       <c r="Y10" s="3">
-        <v>0.29399999999999998</v>
+        <v>0.40500000000000003</v>
       </c>
       <c r="Z10" s="3">
-        <v>0.47099999999999997</v>
+        <v>0.44600000000000001</v>
       </c>
       <c r="AA10" s="2">
-        <v>0.35</v>
+        <v>0.65</v>
       </c>
       <c r="AB10" s="3">
-        <v>0.375</v>
+        <v>0.6</v>
       </c>
       <c r="AC10" s="3">
-        <v>0.222</v>
+        <v>0.24199999999999999</v>
       </c>
       <c r="AD10" s="3">
-        <v>8.5999999999999993E-2</v>
+        <v>0.246</v>
       </c>
       <c r="AE10" s="2">
-        <v>15.8</v>
+        <v>22</v>
       </c>
       <c r="AF10" s="2">
-        <v>0.12</v>
+        <v>0.33</v>
       </c>
       <c r="AG10" s="3">
+        <v>0.45500000000000002</v>
+      </c>
+      <c r="AH10" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="AI10" s="3">
         <v>0</v>
-      </c>
-      <c r="AH10" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="AI10" s="3">
-        <v>0.5</v>
       </c>
     </row>
     <row r="11" spans="1:35" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B11" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C11" s="3">
-        <v>0.35599999999999998</v>
+        <v>0.5</v>
       </c>
       <c r="D11" s="3">
-        <v>0.42199999999999999</v>
+        <v>0.432</v>
       </c>
       <c r="E11" s="4">
-        <v>0.67</v>
+        <v>0.79</v>
       </c>
       <c r="F11" s="3">
-        <v>0.52600000000000002</v>
+        <v>0.746</v>
       </c>
       <c r="G11" s="3">
-        <v>0.23100000000000001</v>
+        <v>0.313</v>
       </c>
       <c r="H11" s="3">
-        <v>0.14499999999999999</v>
+        <v>0.23699999999999999</v>
       </c>
       <c r="I11" s="2">
-        <v>16.2</v>
+        <v>21.9</v>
       </c>
       <c r="J11" s="2">
-        <v>0.38</v>
+        <v>0.25</v>
       </c>
       <c r="K11" s="3">
+        <v>0.42899999999999999</v>
+      </c>
+      <c r="L11" s="3">
+        <v>0.83299999999999996</v>
+      </c>
+      <c r="M11" s="3">
+        <v>0.125</v>
+      </c>
+      <c r="N11" s="3">
+        <v>0.627</v>
+      </c>
+      <c r="O11" s="3">
+        <v>0.56699999999999995</v>
+      </c>
+      <c r="P11" s="2">
+        <v>0.97</v>
+      </c>
+      <c r="Q11" s="3">
+        <v>0.81599999999999995</v>
+      </c>
+      <c r="R11" s="3">
+        <v>0.379</v>
+      </c>
+      <c r="S11" s="3">
+        <v>0.26500000000000001</v>
+      </c>
+      <c r="T11" s="2">
+        <v>30.7</v>
+      </c>
+      <c r="U11" s="2">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="V11" s="3">
+        <v>0.57099999999999995</v>
+      </c>
+      <c r="W11" s="3">
+        <v>1</v>
+      </c>
+      <c r="X11" s="3">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="Y11" s="3">
+        <v>0.39200000000000002</v>
+      </c>
+      <c r="Z11" s="3">
+        <v>0.316</v>
+      </c>
+      <c r="AA11" s="2">
+        <v>0.65</v>
+      </c>
+      <c r="AB11" s="3">
+        <v>0.64</v>
+      </c>
+      <c r="AC11" s="3">
+        <v>0.27800000000000002</v>
+      </c>
+      <c r="AD11" s="3">
+        <v>0.22</v>
+      </c>
+      <c r="AE11" s="2">
+        <v>14.5</v>
+      </c>
+      <c r="AF11" s="2">
+        <v>0.22</v>
+      </c>
+      <c r="AG11" s="3">
+        <v>0.28599999999999998</v>
+      </c>
+      <c r="AH11" s="3">
         <v>0.5</v>
       </c>
-      <c r="L11" s="3">
-        <v>1</v>
-      </c>
-      <c r="M11" s="3">
+      <c r="AI11" s="3">
         <v>0</v>
-      </c>
-      <c r="N11" s="3">
-        <v>0.38900000000000001</v>
-      </c>
-      <c r="O11" s="3">
-        <v>0.61099999999999999</v>
-      </c>
-      <c r="P11" s="2">
-        <v>0.67</v>
-      </c>
-      <c r="Q11" s="3">
-        <v>0.54500000000000004</v>
-      </c>
-      <c r="R11" s="3">
-        <v>0.14299999999999999</v>
-      </c>
-      <c r="S11" s="3">
-        <v>6.5000000000000002E-2</v>
-      </c>
-      <c r="T11" s="2">
-        <v>23</v>
-      </c>
-      <c r="U11" s="2">
-        <v>0.44</v>
-      </c>
-      <c r="V11" s="3">
-        <v>0</v>
-      </c>
-      <c r="W11" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="X11" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y11" s="3">
-        <v>0.33300000000000002</v>
-      </c>
-      <c r="Z11" s="3">
-        <v>0.29599999999999999</v>
-      </c>
-      <c r="AA11" s="2">
-        <v>0.67</v>
-      </c>
-      <c r="AB11" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="AC11" s="3">
-        <v>0.26300000000000001</v>
-      </c>
-      <c r="AD11" s="3">
-        <v>0.191</v>
-      </c>
-      <c r="AE11" s="2">
-        <v>11.7</v>
-      </c>
-      <c r="AF11" s="2">
-        <v>0.33</v>
-      </c>
-      <c r="AG11" s="3">
-        <v>1</v>
-      </c>
-      <c r="AH11" s="3">
-        <v>1</v>
-      </c>
-      <c r="AI11" s="3" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:35" ht="21" customHeight="1" x14ac:dyDescent="0.3">
@@ -1546,403 +1571,963 @@
         <v>23</v>
       </c>
       <c r="B12" s="2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C12" s="3">
-        <v>0.33300000000000002</v>
+        <v>0.48899999999999999</v>
       </c>
       <c r="D12" s="3">
-        <v>0.33300000000000002</v>
+        <v>0.51500000000000001</v>
       </c>
       <c r="E12" s="4">
-        <v>0.69</v>
+        <v>0.71</v>
       </c>
       <c r="F12" s="3">
-        <v>0.46200000000000002</v>
+        <v>0.68600000000000005</v>
       </c>
       <c r="G12" s="3">
-        <v>0.26900000000000002</v>
+        <v>0.27600000000000002</v>
       </c>
       <c r="H12" s="3">
-        <v>0.224</v>
+        <v>0.217</v>
       </c>
       <c r="I12" s="2">
-        <v>19.100000000000001</v>
+        <v>27.6</v>
       </c>
       <c r="J12" s="2">
-        <v>0.05</v>
+        <v>0.31</v>
       </c>
       <c r="K12" s="3">
-        <v>0.25</v>
+        <v>0.59099999999999997</v>
       </c>
       <c r="L12" s="3">
+        <v>0.84599999999999997</v>
+      </c>
+      <c r="M12" s="3">
+        <v>0.111</v>
+      </c>
+      <c r="N12" s="3">
+        <v>0.496</v>
+      </c>
+      <c r="O12" s="3">
+        <v>0.57899999999999996</v>
+      </c>
+      <c r="P12" s="2">
+        <v>0.77</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>0.66700000000000004</v>
+      </c>
+      <c r="R12" s="3">
+        <v>0.255</v>
+      </c>
+      <c r="S12" s="3">
+        <v>0.192</v>
+      </c>
+      <c r="T12" s="2">
+        <v>32.5</v>
+      </c>
+      <c r="U12" s="2">
+        <v>0.31</v>
+      </c>
+      <c r="V12" s="3">
+        <v>0.54500000000000004</v>
+      </c>
+      <c r="W12" s="3">
         <v>1</v>
       </c>
-      <c r="M12" s="3">
-        <v>0</v>
-      </c>
-      <c r="N12" s="3">
+      <c r="X12" s="3">
         <v>0.2</v>
       </c>
-      <c r="O12" s="3">
-        <v>0.53300000000000003</v>
-      </c>
-      <c r="P12" s="2">
-        <v>0.6</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>0.375</v>
-      </c>
-      <c r="R12" s="3">
-        <v>0</v>
-      </c>
-      <c r="S12" s="3">
-        <v>0.14299999999999999</v>
-      </c>
-      <c r="T12" s="2">
-        <v>9</v>
-      </c>
-      <c r="U12" s="2">
-        <v>0</v>
-      </c>
-      <c r="V12" s="3">
-        <v>0</v>
-      </c>
-      <c r="W12" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="X12" s="3">
-        <v>0</v>
-      </c>
       <c r="Y12" s="3">
-        <v>0.41699999999999998</v>
+        <v>0.48099999999999998</v>
       </c>
       <c r="Z12" s="3">
-        <v>0.20799999999999999</v>
+        <v>0.45</v>
       </c>
       <c r="AA12" s="2">
-        <v>0.75</v>
+        <v>0.65</v>
       </c>
       <c r="AB12" s="3">
-        <v>0.6</v>
+        <v>0.71199999999999997</v>
       </c>
       <c r="AC12" s="3">
-        <v>0.36799999999999999</v>
+        <v>0.29199999999999998</v>
       </c>
       <c r="AD12" s="3">
-        <v>0.27100000000000002</v>
+        <v>0.24</v>
       </c>
       <c r="AE12" s="2">
-        <v>25.5</v>
+        <v>22.7</v>
       </c>
       <c r="AF12" s="2">
-        <v>0.08</v>
+        <v>0.31</v>
       </c>
       <c r="AG12" s="3">
-        <v>0.5</v>
+        <v>0.63600000000000001</v>
       </c>
       <c r="AH12" s="3">
-        <v>1</v>
+        <v>0.71399999999999997</v>
       </c>
       <c r="AI12" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:35" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
-      <c r="N13" s="3"/>
-      <c r="O13" s="3"/>
-      <c r="P13" s="2"/>
-      <c r="Q13" s="3"/>
-      <c r="R13" s="3"/>
-      <c r="S13" s="3"/>
-      <c r="T13" s="2"/>
-      <c r="U13" s="2"/>
-      <c r="V13" s="3"/>
-      <c r="W13" s="3"/>
-      <c r="X13" s="3"/>
-      <c r="Y13" s="3"/>
-      <c r="Z13" s="3"/>
-      <c r="AA13" s="2"/>
-      <c r="AB13" s="3"/>
-      <c r="AC13" s="3"/>
-      <c r="AD13" s="3"/>
-      <c r="AE13" s="2"/>
-      <c r="AF13" s="2"/>
-      <c r="AG13" s="3"/>
-      <c r="AH13" s="3"/>
-      <c r="AI13" s="3"/>
+      <c r="A13" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="2">
+        <v>8</v>
+      </c>
+      <c r="C13" s="3">
+        <v>0.48599999999999999</v>
+      </c>
+      <c r="D13" s="3">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="E13" s="4">
+        <v>0.74</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0.70199999999999996</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0.247</v>
+      </c>
+      <c r="H13" s="3">
+        <v>0.192</v>
+      </c>
+      <c r="I13" s="2">
+        <v>16.8</v>
+      </c>
+      <c r="J13" s="2">
+        <v>0.24</v>
+      </c>
+      <c r="K13" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="L13" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="M13" s="3">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="N13" s="3">
+        <v>0.52400000000000002</v>
+      </c>
+      <c r="O13" s="3">
+        <v>0.64300000000000002</v>
+      </c>
+      <c r="P13" s="2">
+        <v>0.87</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>0.70399999999999996</v>
+      </c>
+      <c r="R13" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="S13" s="3">
+        <v>0.187</v>
+      </c>
+      <c r="T13" s="2">
+        <v>21</v>
+      </c>
+      <c r="U13" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="V13" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="W13" s="3">
+        <v>1</v>
+      </c>
+      <c r="X13" s="3">
+        <v>0.66700000000000004</v>
+      </c>
+      <c r="Y13" s="3">
+        <v>0.45300000000000001</v>
+      </c>
+      <c r="Z13" s="3">
+        <v>0.42099999999999999</v>
+      </c>
+      <c r="AA13" s="2">
+        <v>0.63</v>
+      </c>
+      <c r="AB13" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="AC13" s="3">
+        <v>0.27300000000000002</v>
+      </c>
+      <c r="AD13" s="3">
+        <v>0.19500000000000001</v>
+      </c>
+      <c r="AE13" s="2">
+        <v>13.1</v>
+      </c>
+      <c r="AF13" s="2">
+        <v>0.23</v>
+      </c>
+      <c r="AG13" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="AH13" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="1:35" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
-      <c r="N14" s="3"/>
-      <c r="O14" s="3"/>
-      <c r="P14" s="2"/>
-      <c r="Q14" s="3"/>
-      <c r="R14" s="3"/>
-      <c r="S14" s="3"/>
-      <c r="T14" s="2"/>
-      <c r="U14" s="2"/>
-      <c r="V14" s="3"/>
-      <c r="W14" s="3"/>
-      <c r="X14" s="3"/>
-      <c r="Y14" s="3"/>
-      <c r="Z14" s="3"/>
-      <c r="AA14" s="2"/>
-      <c r="AB14" s="3"/>
-      <c r="AC14" s="3"/>
-      <c r="AD14" s="3"/>
-      <c r="AE14" s="2"/>
-      <c r="AF14" s="2"/>
-      <c r="AG14" s="3"/>
-      <c r="AH14" s="3"/>
-      <c r="AI14" s="3"/>
+      <c r="A14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="2">
+        <v>10</v>
+      </c>
+      <c r="C14" s="3">
+        <v>0.47199999999999998</v>
+      </c>
+      <c r="D14" s="3">
+        <v>0.41699999999999998</v>
+      </c>
+      <c r="E14" s="4">
+        <v>0.74</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0.69799999999999995</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0.311</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0.17199999999999999</v>
+      </c>
+      <c r="I14" s="2">
+        <v>27</v>
+      </c>
+      <c r="J14" s="2">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0.16700000000000001</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0.504</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0.48099999999999998</v>
+      </c>
+      <c r="P14" s="2">
+        <v>0.82</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0.76600000000000001</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0.26100000000000001</v>
+      </c>
+      <c r="S14" s="3">
+        <v>0.16300000000000001</v>
+      </c>
+      <c r="T14" s="2">
+        <v>36</v>
+      </c>
+      <c r="U14" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="V14" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="W14" s="3">
+        <v>1</v>
+      </c>
+      <c r="X14" s="3">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>0.438</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>0.34699999999999998</v>
+      </c>
+      <c r="AA14" s="2">
+        <v>0.65</v>
+      </c>
+      <c r="AB14" s="3">
+        <v>0.59499999999999997</v>
+      </c>
+      <c r="AC14" s="3">
+        <v>0.35399999999999998</v>
+      </c>
+      <c r="AD14" s="3">
+        <v>0.18</v>
+      </c>
+      <c r="AE14" s="2">
+        <v>17.2</v>
+      </c>
+      <c r="AF14" s="2">
+        <v>0.38</v>
+      </c>
+      <c r="AG14" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="AH14" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="15" spans="1:35" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
-      <c r="M15" s="3"/>
-      <c r="N15" s="3"/>
-      <c r="O15" s="3"/>
-      <c r="P15" s="2"/>
-      <c r="Q15" s="3"/>
-      <c r="R15" s="3"/>
-      <c r="S15" s="3"/>
-      <c r="T15" s="2"/>
-      <c r="U15" s="2"/>
-      <c r="V15" s="3"/>
-      <c r="W15" s="3"/>
-      <c r="X15" s="3"/>
-      <c r="Y15" s="3"/>
-      <c r="Z15" s="3"/>
-      <c r="AA15" s="2"/>
-      <c r="AB15" s="3"/>
-      <c r="AC15" s="3"/>
-      <c r="AD15" s="3"/>
-      <c r="AE15" s="2"/>
-      <c r="AF15" s="2"/>
-      <c r="AG15" s="3"/>
-      <c r="AH15" s="3"/>
-      <c r="AI15" s="3"/>
+      <c r="A15" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="2">
+        <v>7</v>
+      </c>
+      <c r="C15" s="3">
+        <v>0.49099999999999999</v>
+      </c>
+      <c r="D15" s="3">
+        <v>0.48499999999999999</v>
+      </c>
+      <c r="E15" s="4">
+        <v>0.69</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0.77100000000000002</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0.23300000000000001</v>
+      </c>
+      <c r="H15" s="3">
+        <v>0.20599999999999999</v>
+      </c>
+      <c r="I15" s="2">
+        <v>24.2</v>
+      </c>
+      <c r="J15" s="2">
+        <v>0.21</v>
+      </c>
+      <c r="K15" s="3">
+        <v>0.35699999999999998</v>
+      </c>
+      <c r="L15" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="M15" s="3">
+        <v>0.222</v>
+      </c>
+      <c r="N15" s="3">
+        <v>0.59299999999999997</v>
+      </c>
+      <c r="O15" s="3">
+        <v>0.61599999999999999</v>
+      </c>
+      <c r="P15" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>0.79200000000000004</v>
+      </c>
+      <c r="R15" s="3">
+        <v>0.27300000000000002</v>
+      </c>
+      <c r="S15" s="3">
+        <v>0.249</v>
+      </c>
+      <c r="T15" s="2">
+        <v>28.8</v>
+      </c>
+      <c r="U15" s="2">
+        <v>0.21</v>
+      </c>
+      <c r="V15" s="3">
+        <v>0.28599999999999998</v>
+      </c>
+      <c r="W15" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="X15" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="Y15" s="3">
+        <v>0.39100000000000001</v>
+      </c>
+      <c r="Z15" s="3">
+        <v>0.35299999999999998</v>
+      </c>
+      <c r="AA15" s="2">
+        <v>0.54</v>
+      </c>
+      <c r="AB15" s="3">
+        <v>0.73299999999999998</v>
+      </c>
+      <c r="AC15" s="3">
+        <v>0.21099999999999999</v>
+      </c>
+      <c r="AD15" s="3">
+        <v>0.17199999999999999</v>
+      </c>
+      <c r="AE15" s="2">
+        <v>19.7</v>
+      </c>
+      <c r="AF15" s="2">
+        <v>0.21</v>
+      </c>
+      <c r="AG15" s="3">
+        <v>0.42899999999999999</v>
+      </c>
+      <c r="AH15" s="3">
+        <v>1</v>
+      </c>
+      <c r="AI15" s="3">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="16" spans="1:35" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
-      <c r="M16" s="3"/>
-      <c r="N16" s="3"/>
-      <c r="O16" s="3"/>
-      <c r="P16" s="2"/>
-      <c r="Q16" s="3"/>
-      <c r="R16" s="3"/>
-      <c r="S16" s="3"/>
-      <c r="T16" s="2"/>
-      <c r="U16" s="2"/>
-      <c r="V16" s="3"/>
-      <c r="W16" s="3"/>
-      <c r="X16" s="3"/>
-      <c r="Y16" s="3"/>
-      <c r="Z16" s="3"/>
-      <c r="AA16" s="2"/>
-      <c r="AB16" s="3"/>
-      <c r="AC16" s="3"/>
-      <c r="AD16" s="3"/>
-      <c r="AE16" s="2"/>
-      <c r="AF16" s="2"/>
-      <c r="AG16" s="3"/>
-      <c r="AH16" s="3"/>
-      <c r="AI16" s="3"/>
+      <c r="A16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16" s="2">
+        <v>8</v>
+      </c>
+      <c r="C16" s="3">
+        <v>0.46</v>
+      </c>
+      <c r="D16" s="3">
+        <v>0.50600000000000001</v>
+      </c>
+      <c r="E16" s="4">
+        <v>0.69</v>
+      </c>
+      <c r="F16" s="3">
+        <v>0.64800000000000002</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0.26700000000000002</v>
+      </c>
+      <c r="H16" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="I16" s="2">
+        <v>27</v>
+      </c>
+      <c r="J16" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="K16" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="L16" s="3">
+        <v>0.875</v>
+      </c>
+      <c r="M16" s="3">
+        <v>0.125</v>
+      </c>
+      <c r="N16" s="3">
+        <v>0.46200000000000002</v>
+      </c>
+      <c r="O16" s="3">
+        <v>0.60299999999999998</v>
+      </c>
+      <c r="P16" s="2">
+        <v>0.73</v>
+      </c>
+      <c r="Q16" s="3">
+        <v>0.61699999999999999</v>
+      </c>
+      <c r="R16" s="3">
+        <v>0.22600000000000001</v>
+      </c>
+      <c r="S16" s="3">
+        <v>0.17399999999999999</v>
+      </c>
+      <c r="T16" s="2">
+        <v>33.200000000000003</v>
+      </c>
+      <c r="U16" s="2">
+        <v>0.13</v>
+      </c>
+      <c r="V16" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="W16" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="X16" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="3">
+        <v>0.45800000000000002</v>
+      </c>
+      <c r="Z16" s="3">
+        <v>0.42699999999999999</v>
+      </c>
+      <c r="AA16" s="2">
+        <v>0.66</v>
+      </c>
+      <c r="AB16" s="3">
+        <v>0.68300000000000005</v>
+      </c>
+      <c r="AC16" s="3">
+        <v>0.29099999999999998</v>
+      </c>
+      <c r="AD16" s="3">
+        <v>0.22</v>
+      </c>
+      <c r="AE16" s="2">
+        <v>21.9</v>
+      </c>
+      <c r="AF16" s="2">
+        <v>0.26</v>
+      </c>
+      <c r="AG16" s="3">
+        <v>0.375</v>
+      </c>
+      <c r="AH16" s="3">
+        <v>1</v>
+      </c>
+      <c r="AI16" s="3">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="17" spans="1:35" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="3"/>
-      <c r="L17" s="3"/>
-      <c r="M17" s="3"/>
-      <c r="N17" s="3"/>
-      <c r="O17" s="3"/>
-      <c r="P17" s="2"/>
-      <c r="Q17" s="3"/>
-      <c r="R17" s="3"/>
-      <c r="S17" s="3"/>
-      <c r="T17" s="2"/>
-      <c r="U17" s="2"/>
-      <c r="V17" s="3"/>
-      <c r="W17" s="3"/>
-      <c r="X17" s="3"/>
-      <c r="Y17" s="3"/>
-      <c r="Z17" s="3"/>
-      <c r="AA17" s="2"/>
-      <c r="AB17" s="3"/>
-      <c r="AC17" s="3"/>
-      <c r="AD17" s="3"/>
-      <c r="AE17" s="2"/>
-      <c r="AF17" s="2"/>
-      <c r="AG17" s="3"/>
-      <c r="AH17" s="3"/>
-      <c r="AI17" s="3"/>
+      <c r="A17" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17" s="2">
+        <v>5</v>
+      </c>
+      <c r="C17" s="3">
+        <v>0.43099999999999999</v>
+      </c>
+      <c r="D17" s="3">
+        <v>0.45700000000000002</v>
+      </c>
+      <c r="E17" s="4">
+        <v>0.72</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0.623</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0.27</v>
+      </c>
+      <c r="H17" s="3">
+        <v>0.17299999999999999</v>
+      </c>
+      <c r="I17" s="2">
+        <v>20.7</v>
+      </c>
+      <c r="J17" s="2">
+        <v>0.39</v>
+      </c>
+      <c r="K17" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="L17" s="3">
+        <v>0.83299999999999996</v>
+      </c>
+      <c r="M17" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="N17" s="3">
+        <v>0.41299999999999998</v>
+      </c>
+      <c r="O17" s="3">
+        <v>0.55600000000000005</v>
+      </c>
+      <c r="P17" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>0.54300000000000004</v>
+      </c>
+      <c r="R17" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="S17" s="3">
+        <v>0.127</v>
+      </c>
+      <c r="T17" s="2">
+        <v>22.3</v>
+      </c>
+      <c r="U17" s="2">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="V17" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="W17" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="X17" s="3">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="Y17" s="3">
+        <v>0.45300000000000001</v>
+      </c>
+      <c r="Z17" s="3">
+        <v>0.34</v>
+      </c>
+      <c r="AA17" s="2">
+        <v>0.68</v>
+      </c>
+      <c r="AB17" s="3">
+        <v>0.77800000000000002</v>
+      </c>
+      <c r="AC17" s="3">
+        <v>0.28599999999999998</v>
+      </c>
+      <c r="AD17" s="3">
+        <v>0.22700000000000001</v>
+      </c>
+      <c r="AE17" s="2">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="AF17" s="2">
+        <v>0.51</v>
+      </c>
+      <c r="AG17" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="AH17" s="3">
+        <v>1</v>
+      </c>
+      <c r="AI17" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="18" spans="1:35" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="3"/>
-      <c r="L18" s="3"/>
-      <c r="M18" s="3"/>
-      <c r="N18" s="3"/>
-      <c r="O18" s="3"/>
-      <c r="P18" s="2"/>
-      <c r="Q18" s="3"/>
-      <c r="R18" s="3"/>
-      <c r="S18" s="3"/>
-      <c r="T18" s="2"/>
-      <c r="U18" s="2"/>
-      <c r="V18" s="3"/>
-      <c r="W18" s="3"/>
-      <c r="X18" s="3"/>
-      <c r="Y18" s="3"/>
-      <c r="Z18" s="3"/>
-      <c r="AA18" s="2"/>
-      <c r="AB18" s="3"/>
-      <c r="AC18" s="3"/>
-      <c r="AD18" s="3"/>
-      <c r="AE18" s="2"/>
-      <c r="AF18" s="2"/>
-      <c r="AG18" s="3"/>
-      <c r="AH18" s="3"/>
-      <c r="AI18" s="3"/>
+      <c r="A18" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B18" s="2">
+        <v>5</v>
+      </c>
+      <c r="C18" s="3">
+        <v>0.35299999999999998</v>
+      </c>
+      <c r="D18" s="3">
+        <v>0.48499999999999999</v>
+      </c>
+      <c r="E18" s="4">
+        <v>0.53</v>
+      </c>
+      <c r="F18" s="3">
+        <v>0.51</v>
+      </c>
+      <c r="G18" s="3">
+        <v>0.20799999999999999</v>
+      </c>
+      <c r="H18" s="3">
+        <v>0.13600000000000001</v>
+      </c>
+      <c r="I18" s="2">
+        <v>20.8</v>
+      </c>
+      <c r="J18" s="2">
+        <v>0.27</v>
+      </c>
+      <c r="K18" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="L18" s="3">
+        <v>1</v>
+      </c>
+      <c r="M18" s="3">
+        <v>0.111</v>
+      </c>
+      <c r="N18" s="3">
+        <v>0.35099999999999998</v>
+      </c>
+      <c r="O18" s="3">
+        <v>0.57099999999999995</v>
+      </c>
+      <c r="P18" s="2">
+        <v>0.54</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="R18" s="3">
+        <v>0.16</v>
+      </c>
+      <c r="S18" s="3">
+        <v>0.122</v>
+      </c>
+      <c r="T18" s="2">
+        <v>24.4</v>
+      </c>
+      <c r="U18" s="2">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="V18" s="3">
+        <v>0</v>
+      </c>
+      <c r="W18" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="X18" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="Y18" s="3">
+        <v>0.35599999999999998</v>
+      </c>
+      <c r="Z18" s="3">
+        <v>0.378</v>
+      </c>
+      <c r="AA18" s="2">
+        <v>0.51</v>
+      </c>
+      <c r="AB18" s="3">
+        <v>0.52900000000000003</v>
+      </c>
+      <c r="AC18" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="AD18" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="AE18" s="2">
+        <v>16.2</v>
+      </c>
+      <c r="AF18" s="2">
+        <v>0.27</v>
+      </c>
+      <c r="AG18" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="AH18" s="3">
+        <v>1</v>
+      </c>
+      <c r="AI18" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="19" spans="1:35" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="3"/>
-      <c r="L19" s="3"/>
-      <c r="M19" s="3"/>
-      <c r="N19" s="3"/>
-      <c r="O19" s="3"/>
-      <c r="P19" s="2"/>
-      <c r="Q19" s="3"/>
-      <c r="R19" s="3"/>
-      <c r="S19" s="3"/>
-      <c r="T19" s="2"/>
-      <c r="U19" s="2"/>
-      <c r="V19" s="3"/>
-      <c r="W19" s="3"/>
-      <c r="X19" s="3"/>
-      <c r="Y19" s="3"/>
-      <c r="Z19" s="3"/>
-      <c r="AA19" s="2"/>
-      <c r="AB19" s="3"/>
-      <c r="AC19" s="3"/>
-      <c r="AD19" s="3"/>
-      <c r="AE19" s="2"/>
-      <c r="AF19" s="2"/>
-      <c r="AG19" s="3"/>
-      <c r="AH19" s="3"/>
-      <c r="AI19" s="3"/>
+      <c r="A19" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B19" s="2">
+        <v>5</v>
+      </c>
+      <c r="C19" s="3">
+        <v>0.44900000000000001</v>
+      </c>
+      <c r="D19" s="3">
+        <v>0.439</v>
+      </c>
+      <c r="E19" s="4">
+        <v>0.71</v>
+      </c>
+      <c r="F19" s="3">
+        <v>0.61699999999999999</v>
+      </c>
+      <c r="G19" s="3">
+        <v>0.317</v>
+      </c>
+      <c r="H19" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="I19" s="2">
+        <v>26.7</v>
+      </c>
+      <c r="J19" s="2">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="K19" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="L19" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="M19" s="3">
+        <v>0.16700000000000001</v>
+      </c>
+      <c r="N19" s="3">
+        <v>0.40699999999999997</v>
+      </c>
+      <c r="O19" s="3">
+        <v>0.50800000000000001</v>
+      </c>
+      <c r="P19" s="2">
+        <v>0.66</v>
+      </c>
+      <c r="Q19" s="3">
+        <v>0.63300000000000001</v>
+      </c>
+      <c r="R19" s="3">
+        <v>0.17199999999999999</v>
+      </c>
+      <c r="S19" s="3">
+        <v>0.156</v>
+      </c>
+      <c r="T19" s="2">
+        <v>28.4</v>
+      </c>
+      <c r="U19" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="V19" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="W19" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="X19" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="Z19" s="3">
+        <v>0.35399999999999998</v>
+      </c>
+      <c r="AA19" s="2">
+        <v>0.77</v>
+      </c>
+      <c r="AB19" s="3">
+        <v>0.58799999999999997</v>
+      </c>
+      <c r="AC19" s="3">
+        <v>0.45200000000000001</v>
+      </c>
+      <c r="AD19" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="AE19" s="2">
+        <v>24.6</v>
+      </c>
+      <c r="AF19" s="2">
+        <v>0.38</v>
+      </c>
+      <c r="AG19" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="AH19" s="3">
+        <v>1</v>
+      </c>
+      <c r="AI19" s="3">
+        <v>0.33300000000000002</v>
+      </c>
     </row>
     <row r="20" spans="1:35" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="3"/>
-      <c r="L20" s="3"/>
-      <c r="M20" s="3"/>
-      <c r="N20" s="3"/>
-      <c r="O20" s="3"/>
-      <c r="P20" s="2"/>
-      <c r="Q20" s="3"/>
-      <c r="R20" s="3"/>
-      <c r="S20" s="3"/>
-      <c r="T20" s="2"/>
-      <c r="U20" s="2"/>
-      <c r="V20" s="3"/>
-      <c r="W20" s="3"/>
-      <c r="X20" s="3"/>
-      <c r="Y20" s="3"/>
-      <c r="Z20" s="3"/>
-      <c r="AA20" s="2"/>
-      <c r="AB20" s="3"/>
-      <c r="AC20" s="3"/>
-      <c r="AD20" s="3"/>
-      <c r="AE20" s="2"/>
-      <c r="AF20" s="2"/>
-      <c r="AG20" s="3"/>
-      <c r="AH20" s="3"/>
-      <c r="AI20" s="3"/>
+      <c r="A20" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B20" s="2">
+        <v>4</v>
+      </c>
+      <c r="C20" s="3">
+        <v>0.25700000000000001</v>
+      </c>
+      <c r="D20" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="E20" s="4">
+        <v>0.54</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0.39300000000000002</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0.16700000000000001</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0.13700000000000001</v>
+      </c>
+      <c r="I20" s="2">
+        <v>15</v>
+      </c>
+      <c r="J20" s="2">
+        <v>0.16</v>
+      </c>
+      <c r="K20" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="L20" s="3">
+        <v>1</v>
+      </c>
+      <c r="M20" s="3">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="N20" s="3">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="O20" s="3">
+        <v>0.51600000000000001</v>
+      </c>
+      <c r="P20" s="2">
+        <v>0.65</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="R20" s="3">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="S20" s="3">
+        <v>0.10299999999999999</v>
+      </c>
+      <c r="T20" s="2">
+        <v>20</v>
+      </c>
+      <c r="U20" s="2">
+        <v>0.13</v>
+      </c>
+      <c r="V20" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="W20" s="3">
+        <v>1</v>
+      </c>
+      <c r="X20" s="3">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="Y20" s="3">
+        <v>0.23100000000000001</v>
+      </c>
+      <c r="Z20" s="3">
+        <v>0.308</v>
+      </c>
+      <c r="AA20" s="2">
+        <v>0.46</v>
+      </c>
+      <c r="AB20" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="AC20" s="3">
+        <v>0.222</v>
+      </c>
+      <c r="AD20" s="3">
+        <v>0.16</v>
+      </c>
+      <c r="AE20" s="2">
+        <v>11.1</v>
+      </c>
+      <c r="AF20" s="2">
+        <v>0.18</v>
+      </c>
+      <c r="AG20" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="AH20" s="3">
+        <v>1</v>
+      </c>
+      <c r="AI20" s="3">
+        <v>0.33300000000000002</v>
+      </c>
     </row>
     <row r="21" spans="1:35" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2"/>
